--- a/data/trans_camb/IP1006-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP1006-Clase-trans_camb.xlsx
@@ -641,7 +641,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,77</t>
+          <t>0,0; 3,71</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -943,7 +943,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,08</t>
+          <t>0,0; 4,61</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -953,22 +953,22 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,47; 0,0</t>
+          <t>-3,53; 0,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 2,64</t>
+          <t>-1,41; 2,65</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 0,8</t>
+          <t>-1,26; 0,81</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 1,44</t>
+          <t>-0,84; 1,47</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 0,97</t>
+          <t>-0,64; 1,11</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 0,54</t>
+          <t>-1,11; 0,54</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 2,44</t>
+          <t>-0,35; 2,31</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 0,0</t>
+          <t>-1,7; 0,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 1,28</t>
+          <t>-0,32; 1,4</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 0,25</t>
+          <t>-0,91; 0,26</t>
         </is>
       </c>
     </row>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-80,5; —</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 0,0</t>
+          <t>-3,3; 0,0</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 3,26</t>
+          <t>-1,02; 3,32</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 4,14</t>
+          <t>-0,59; 4,0</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 0,88</t>
+          <t>-2,26; 0,88</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 1,8</t>
+          <t>-0,99; 1,67</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 1,72</t>
+          <t>-0,9; 1,6</t>
         </is>
       </c>
     </row>
@@ -1411,12 +1411,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-3,59; 0,0</t>
+          <t>-3,58; 0,0</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 0,0</t>
+          <t>-3,57; 0,0</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1426,17 +1426,17 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,49</t>
+          <t>0,0; 7,77</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 0,0</t>
+          <t>-2,01; 0,0</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 2,29</t>
+          <t>-0,71; 2,3</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 0,3</t>
+          <t>-0,58; 0,31</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 0,65</t>
+          <t>-0,39; 0,64</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 1,25</t>
+          <t>-0,04; 1,28</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 0,41</t>
+          <t>-0,52; 0,41</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 0,68</t>
+          <t>-0,13; 0,68</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 0,39</t>
+          <t>-0,29; 0,38</t>
         </is>
       </c>
     </row>
@@ -1648,12 +1648,12 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-98,59; —</t>
+          <t>-90,32; —</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-41,37; —</t>
+          <t>-35,97; 1451,3</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -1663,12 +1663,12 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-34,39; 521,09</t>
+          <t>-44,16; 528,25</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-67,87; 290,43</t>
+          <t>-71,29; 258,5</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1006-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP1006-Clase-trans_camb.xlsx
@@ -641,7 +641,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,71</t>
+          <t>0,0; 4,03</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,88</t>
+          <t>0,0; 1,91</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -943,7 +943,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,61</t>
+          <t>0,0; 3,58</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -953,22 +953,22 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 0,0</t>
+          <t>-4,18; 0,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 2,65</t>
+          <t>-1,42; 2,61</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 0,81</t>
+          <t>-1,26; 0,8</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 1,47</t>
+          <t>-0,83; 1,41</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 1,11</t>
+          <t>-0,64; 0,98</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 0,54</t>
+          <t>-1,01; 0,75</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 2,31</t>
+          <t>-0,38; 2,35</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 0,0</t>
+          <t>-1,92; 0,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 1,4</t>
+          <t>-0,35; 1,28</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 0,26</t>
+          <t>-0,99; 0,14</t>
         </is>
       </c>
     </row>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-80,5; —</t>
+          <t>-94,41; —</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 0,0</t>
+          <t>-3,31; 0,0</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 3,32</t>
+          <t>-1,32; 3,18</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 4,0</t>
+          <t>-0,64; 4,33</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 0,88</t>
+          <t>-1,85; 0,89</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 1,67</t>
+          <t>-0,96; 1,67</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 1,6</t>
+          <t>-0,84; 1,69</t>
         </is>
       </c>
     </row>
@@ -1411,12 +1411,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 0,0</t>
+          <t>-3,53; 0,0</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-3,57; 0,0</t>
+          <t>-4,13; 0,0</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1426,17 +1426,17 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,77</t>
+          <t>0,0; 5,06</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 0,0</t>
+          <t>-1,79; 0,0</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 2,3</t>
+          <t>-0,71; 2,29</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 0,31</t>
+          <t>-0,5; 0,3</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 0,64</t>
+          <t>-0,39; 0,61</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 1,28</t>
+          <t>-0,06; 1,26</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 0,41</t>
+          <t>-0,51; 0,44</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 0,68</t>
+          <t>-0,14; 0,66</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 0,38</t>
+          <t>-0,31; 0,37</t>
         </is>
       </c>
     </row>
@@ -1648,12 +1648,12 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-90,32; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-35,97; 1451,3</t>
+          <t>-40,53; 1128,64</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -1663,12 +1663,12 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-44,16; 528,25</t>
+          <t>-42,59; 484,48</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-71,29; 258,5</t>
+          <t>-72,35; 322,28</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1006-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP1006-Clase-trans_camb.xlsx
@@ -519,13 +519,13 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -593,17 +593,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,74</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,74</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -631,7 +631,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 3,77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,03</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,91</t>
+          <t>0,0; 1,88</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -669,17 +669,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -905,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-0,7</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0,14</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>0,81</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-0,7</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,14</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,58</t>
+          <t>-3,47; 0,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-1,42; 2,64</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,18; 0,0</t>
+          <t>0,0; 4,08</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 2,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 0,8</t>
+          <t>-1,66; 0,8</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 1,41</t>
+          <t>-0,84; 1,44</t>
         </is>
       </c>
     </row>
@@ -981,22 +981,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>20,09%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>20,09%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0,85</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-0,34</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>-0,05</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0,85</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-0,34</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 0,98</t>
+          <t>-0,34; 2,44</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 0,75</t>
+          <t>-1,94; 0,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 2,35</t>
+          <t>-0,64; 0,97</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 0,0</t>
+          <t>-0,96; 0,54</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 1,28</t>
+          <t>-0,36; 1,28</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 0,14</t>
+          <t>-0,86; 0,25</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>251,01%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>0,5%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>-16,04%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>251,01%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-94,41; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>1,24</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-0,13</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>-0,66</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>0,87</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>1,24</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-0,13</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 0,0</t>
+          <t>-0,7; 4,14</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 3,18</t>
+          <t>-1,82; 0,88</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 4,33</t>
+          <t>-3,29; 0,0</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 0,89</t>
+          <t>-1,29; 3,26</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 1,67</t>
+          <t>-0,9; 1,8</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 1,69</t>
+          <t>-0,94; 1,72</t>
         </is>
       </c>
     </row>
@@ -1293,22 +1293,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>218,73%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-22,68%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>131,88%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>218,73%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-22,68%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1373,22 +1373,22 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>1,09</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
           <t>-0,7</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>-0,7</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>1,09</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1411,27 +1411,27 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-4,13; 0,0</t>
+          <t>0,0; 5,49</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-3,59; 0,0</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,06</t>
+          <t>-3,68; 0,0</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 0,0</t>
+          <t>-2,16; 0,0</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1449,22 +1449,22 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1529,22 +1529,22 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>0,52</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>-0,03</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
           <t>-0,09</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>0,11</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>0,52</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>-0,03</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 0,3</t>
+          <t>-0,1; 1,25</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 0,61</t>
+          <t>-0,53; 0,41</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 1,26</t>
+          <t>-0,59; 0,3</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 0,44</t>
+          <t>-0,41; 0,65</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 0,66</t>
+          <t>-0,11; 0,68</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 0,37</t>
+          <t>-0,3; 0,39</t>
         </is>
       </c>
     </row>
@@ -1605,22 +1605,22 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>169,05%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>-8,18%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
           <t>-31,02%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>37,55%</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>169,05%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>-8,18%</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-41,37; —</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-40,53; 1128,64</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-98,59; —</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-42,59; 484,48</t>
+          <t>-34,39; 521,09</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-72,35; 322,28</t>
+          <t>-67,87; 290,43</t>
         </is>
       </c>
     </row>
